--- a/data/sources_list_.xlsx
+++ b/data/sources_list_.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/clara/Downloads/RE_ ML for AWH Discussion/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8C2B54-029F-2C49-9E70-7E63AA0FDF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02B7F5B-3BF7-574C-82A2-E6AF1C69B4CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13600" yWindow="760" windowWidth="16640" windowHeight="17760" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Sources" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="501">
   <si>
     <t xml:space="preserve">Data Source </t>
   </si>
@@ -1467,13 +1467,85 @@
   </si>
   <si>
     <t>Paper 25 (NaBrO3)</t>
+  </si>
+  <si>
+    <t> Kinematic viscosity and water activity of aqueous solutions of glycerol and sodium chloride</t>
+  </si>
+  <si>
+    <t>Glycerol &amp; NaCl</t>
+  </si>
+  <si>
+    <t>Paper 26 (Glycerol, C3H8O3)</t>
+  </si>
+  <si>
+    <t>Activity and Activity Coefficient of Water in Aqueous Solutions and Their Relationships with Solution Structure Parameters</t>
+  </si>
+  <si>
+    <t>Urea, sucrose</t>
+  </si>
+  <si>
+    <t>Calculated from freezing point depression; Taken from figure 2 using automeris</t>
+  </si>
+  <si>
+    <t>mol fraction</t>
+  </si>
+  <si>
+    <t>Paper 27 (Urea, CO(NH2)2)</t>
+  </si>
+  <si>
+    <t>Paper 27 (Sucrose, C12H22O11)</t>
+  </si>
+  <si>
+    <t>Water activity and mobility in solutions of glycerol and small molecular weight sugars: Implication for cryo- and lyopreservation</t>
+  </si>
+  <si>
+    <t>fructose</t>
+  </si>
+  <si>
+    <t>Paper 28 (Fructose, C6H12O6)</t>
+  </si>
+  <si>
+    <t>water mass fraction</t>
+  </si>
+  <si>
+    <t>Dataset of water activity measurements of alcohol:water solutions using a Tunable Diode Laser</t>
+  </si>
+  <si>
+    <t>methanol, ethanol</t>
+  </si>
+  <si>
+    <t>Using a tunable diode laser</t>
+  </si>
+  <si>
+    <t>Paper 29 (Ethanol, C2H6O)</t>
+  </si>
+  <si>
+    <t>Paper 29 (Methanol, CH3OH)</t>
+  </si>
+  <si>
+    <t>Osmotic properties of carbohydrate aqueous solutions</t>
+  </si>
+  <si>
+    <t>carbohydrates</t>
+  </si>
+  <si>
+    <t>Paper 30 (D (+) – Xylose )</t>
+  </si>
+  <si>
+    <t>Paper 30 (L (+) – Arabinose )</t>
+  </si>
+  <si>
+    <t>Paper 30 (Xylitol )</t>
+  </si>
+  <si>
+    <t>Paper 30 (Glucose )</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1759,8 +1831,8 @@
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>17417</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>591348</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>5195</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2305,7 +2377,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="25.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="25.5" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="25.5" style="2" customWidth="1"/>
     <col min="5" max="8" width="13.1640625" style="2" customWidth="1"/>
@@ -2313,7 +2385,7 @@
     <col min="10" max="16384" width="25.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2345,7 +2417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="96" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
@@ -2377,7 +2449,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="80" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
@@ -2406,7 +2478,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="80" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>27</v>
       </c>
@@ -2426,7 +2498,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="80" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>32</v>
       </c>
@@ -2449,7 +2521,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="48" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>38</v>
       </c>
@@ -2463,7 +2535,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="80" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>41</v>
       </c>
@@ -2474,7 +2546,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="48" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>43</v>
       </c>
@@ -2491,7 +2563,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="48" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>46</v>
       </c>
@@ -2517,7 +2589,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="160" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="160" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>53</v>
       </c>
@@ -2546,7 +2618,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="80" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>60</v>
       </c>
@@ -2569,10 +2641,10 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="16" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>65</v>
       </c>
@@ -2586,7 +2658,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="48" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>68</v>
       </c>
@@ -2607,7 +2679,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="16" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>73</v>
       </c>
@@ -2616,7 +2688,7 @@
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="16" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>74</v>
       </c>
@@ -2624,12 +2696,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="16" customHeight="1">
       <c r="C24" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="48" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>76</v>
       </c>
@@ -2652,7 +2724,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="96" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>83</v>
       </c>
@@ -2681,10 +2753,10 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="1"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
     </row>
@@ -2713,7 +2785,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="25.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="25.5" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="25.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="2" customWidth="1"/>
@@ -2724,7 +2796,7 @@
     <col min="11" max="16384" width="25.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>90</v>
       </c>
@@ -2747,7 +2819,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>95</v>
       </c>
@@ -2764,7 +2836,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="48" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>98</v>
       </c>
@@ -2781,7 +2853,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="64" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>101</v>
       </c>
@@ -2801,7 +2873,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="64" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>104</v>
       </c>
@@ -2818,7 +2890,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="320" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="320" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>107</v>
       </c>
@@ -2838,7 +2910,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="80" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>110</v>
       </c>
@@ -2855,10 +2927,10 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="64" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>113</v>
       </c>
@@ -2875,7 +2947,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="64" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>116</v>
       </c>
@@ -2898,7 +2970,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="64" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>121</v>
       </c>
@@ -2927,7 +2999,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="80" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>126</v>
       </c>
@@ -2950,7 +3022,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="96" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="96">
       <c r="A13" s="4" t="s">
         <v>405</v>
       </c>
@@ -2967,7 +3039,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="48">
       <c r="A14" s="4" t="s">
         <v>408</v>
       </c>
@@ -3011,7 +3083,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="25.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="25.5" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="25.5" style="2" customWidth="1"/>
     <col min="3" max="3" width="13.1640625" style="2" customWidth="1"/>
@@ -3019,7 +3091,7 @@
     <col min="5" max="16384" width="25.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="16" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>90</v>
       </c>
@@ -3030,7 +3102,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="32" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>130</v>
       </c>
@@ -3038,7 +3110,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="112" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>131</v>
       </c>
@@ -3049,7 +3121,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="48" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>132</v>
       </c>
@@ -3060,7 +3132,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="48" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>404</v>
       </c>
@@ -3071,7 +3143,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="64">
       <c r="A7" s="4" t="s">
         <v>386</v>
       </c>
@@ -3082,7 +3154,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="64">
       <c r="A8" s="4" t="s">
         <v>388</v>
       </c>
@@ -3093,7 +3165,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="80">
       <c r="A9" s="4" t="s">
         <v>392</v>
       </c>
@@ -3104,7 +3176,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="80">
       <c r="A10" s="4" t="s">
         <v>394</v>
       </c>
@@ -3115,7 +3187,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="64">
       <c r="A11" s="4" t="s">
         <v>396</v>
       </c>
@@ -3126,7 +3198,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="48">
       <c r="A12" s="9" t="s">
         <v>397</v>
       </c>
@@ -3137,7 +3209,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="32">
       <c r="A13" s="9" t="s">
         <v>399</v>
       </c>
@@ -3148,7 +3220,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="16">
       <c r="A14" s="9" t="s">
         <v>401</v>
       </c>
@@ -3162,7 +3234,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="32">
       <c r="A15" s="9" t="s">
         <v>405</v>
       </c>
@@ -3173,7 +3245,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="32">
       <c r="A16" s="9" t="s">
         <v>410</v>
       </c>
@@ -3184,7 +3256,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="64">
       <c r="A17" s="2" t="s">
         <v>412</v>
       </c>
@@ -3218,8 +3290,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:NO54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="20.5" defaultRowHeight="49" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:PC54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="20.5" defaultRowHeight="49" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.5" style="2" customWidth="1"/>
@@ -3229,11 +3301,11 @@
     <col min="8" max="8" width="7.5" style="2" customWidth="1"/>
     <col min="9" max="14" width="8.5" style="2" customWidth="1"/>
     <col min="15" max="15" width="8.5" style="6" customWidth="1"/>
-    <col min="16" max="386" width="8.5" style="2" customWidth="1"/>
-    <col min="387" max="16384" width="20.5" style="2"/>
+    <col min="16" max="474" width="8.5" style="2" customWidth="1"/>
+    <col min="475" max="16384" width="20.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:379" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:419" s="1" customFormat="1" ht="49" customHeight="1">
       <c r="B1" t="s">
         <v>133</v>
       </c>
@@ -3530,8 +3602,38 @@
       <c r="NL1" s="1">
         <v>150.88999999999999</v>
       </c>
+      <c r="NQ1" s="1">
+        <v>92.09</v>
+      </c>
+      <c r="NU1" s="1">
+        <v>342.3</v>
+      </c>
+      <c r="NY1" s="1">
+        <v>60.06</v>
+      </c>
+      <c r="OC1" s="1">
+        <v>180.16</v>
+      </c>
+      <c r="OG1" s="1">
+        <v>46.07</v>
+      </c>
+      <c r="OK1" s="1">
+        <v>32.04</v>
+      </c>
+      <c r="OO1" s="1">
+        <v>150.13</v>
+      </c>
+      <c r="OS1" s="1">
+        <v>150.13</v>
+      </c>
+      <c r="OW1" s="1">
+        <v>152.15</v>
+      </c>
+      <c r="PA1" s="1">
+        <v>180.16</v>
+      </c>
     </row>
-    <row r="2" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:419" ht="49" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>457</v>
       </c>
@@ -3844,8 +3946,48 @@
         <f>NL1/1000</f>
         <v>0.15089</v>
       </c>
+      <c r="NQ2" s="2">
+        <f>NQ1/1000</f>
+        <v>9.2090000000000005E-2</v>
+      </c>
+      <c r="NU2" s="2">
+        <f>NU1/1000</f>
+        <v>0.34229999999999999</v>
+      </c>
+      <c r="NY2" s="2">
+        <f>NY1/1000</f>
+        <v>6.0060000000000002E-2</v>
+      </c>
+      <c r="OC2" s="2">
+        <f>OC1/1000</f>
+        <v>0.18015999999999999</v>
+      </c>
+      <c r="OG2" s="2">
+        <f>OG1/1000</f>
+        <v>4.607E-2</v>
+      </c>
+      <c r="OK2" s="2">
+        <f>OK1/1000</f>
+        <v>3.2039999999999999E-2</v>
+      </c>
+      <c r="OO2" s="2">
+        <f>OO1/1000</f>
+        <v>0.15012999999999999</v>
+      </c>
+      <c r="OS2" s="2">
+        <f>OS1/1000</f>
+        <v>0.15012999999999999</v>
+      </c>
+      <c r="OW2" s="2">
+        <f>OW1/1000</f>
+        <v>0.15215000000000001</v>
+      </c>
+      <c r="PA2" s="2">
+        <f>PA1/1000</f>
+        <v>0.18015999999999999</v>
+      </c>
     </row>
-    <row r="3" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:419" ht="49" customHeight="1">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -4025,7 +4167,7 @@
         <v>8.0043000000000003E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:419" ht="49" customHeight="1">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -4271,8 +4413,38 @@
       <c r="NL4" s="10" t="s">
         <v>476</v>
       </c>
+      <c r="NQ4" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="NU4" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="NY4" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="OC4" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="OG4" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="OK4" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="OO4" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="OS4" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="OW4" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="PA4" s="10" t="s">
+        <v>500</v>
+      </c>
     </row>
-    <row r="5" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:419" ht="49" customHeight="1">
       <c r="T5" s="2" t="s">
         <v>207</v>
       </c>
@@ -4298,7 +4470,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="6" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:419" ht="49" customHeight="1">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -4411,7 +4583,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="7" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:419" ht="49" customHeight="1">
       <c r="P7" s="2">
         <v>0.1</v>
       </c>
@@ -5298,8 +5470,98 @@
       <c r="NO7" s="2" t="s">
         <v>238</v>
       </c>
+      <c r="NQ7" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="NR7" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="NS7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="NU7" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="NV7" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="NW7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="NY7" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="NZ7" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="OA7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="OC7" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="OD7" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="OE7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="OG7" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="OH7" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="OI7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="OK7" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="OL7" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="OM7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="OO7" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="OP7" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="OQ7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="OS7" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="OT7" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="OU7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="OW7" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="OX7" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="OY7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="PA7" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="PB7" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="PC7" s="2" t="s">
+        <v>238</v>
+      </c>
     </row>
-    <row r="8" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:419" ht="49" customHeight="1">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -6310,8 +6572,108 @@
         <f>EXP(-2*NL8*NN8/55.51)</f>
         <v>0.99669795163285935</v>
       </c>
+      <c r="NQ8" s="2">
+        <v>0</v>
+      </c>
+      <c r="NR8" s="2">
+        <f>$NQ$2*NQ8/(1+$NQ$2*NQ8)</f>
+        <v>0</v>
+      </c>
+      <c r="NS8">
+        <v>1</v>
+      </c>
+      <c r="NU8" s="2">
+        <v>0</v>
+      </c>
+      <c r="NV8" s="2">
+        <f>NU8 * $NU$2/(NU8 * $NU$2+(1-NU8)*$BI$3)</f>
+        <v>0</v>
+      </c>
+      <c r="NW8">
+        <v>1</v>
+      </c>
+      <c r="NY8" s="2">
+        <v>0</v>
+      </c>
+      <c r="NZ8" s="2">
+        <f>NY8 * $NY$2/(NY8 * $NY$2+(1-NY8)*$BI$3)</f>
+        <v>0</v>
+      </c>
+      <c r="OA8">
+        <v>1</v>
+      </c>
+      <c r="OC8" s="2">
+        <v>0.98099999999999998</v>
+      </c>
+      <c r="OD8" s="2">
+        <f>1-OC8</f>
+        <v>1.9000000000000017E-2</v>
+      </c>
+      <c r="OE8">
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="OG8" s="2">
+        <v>0</v>
+      </c>
+      <c r="OH8" s="2">
+        <f>OG8 * $OG$2/(OG8 * $OG$2+(1-OG8)*$BI$3)</f>
+        <v>0</v>
+      </c>
+      <c r="OI8">
+        <v>1</v>
+      </c>
+      <c r="OK8" s="2">
+        <v>0</v>
+      </c>
+      <c r="OL8" s="2">
+        <f>OK8 * $OG$2/(OK8 * $OG$2+(1-OK8)*$BI$3)</f>
+        <v>0</v>
+      </c>
+      <c r="OM8">
+        <v>1</v>
+      </c>
+      <c r="OO8" s="2">
+        <v>6.7199999999999996E-2</v>
+      </c>
+      <c r="OP8" s="2">
+        <f>$OO$2*OO8/(1+$OO$2*OO8)</f>
+        <v>9.987970007419229E-3</v>
+      </c>
+      <c r="OQ8">
+        <v>0.99880000000000002</v>
+      </c>
+      <c r="OS8" s="2">
+        <v>3.32E-2</v>
+      </c>
+      <c r="OT8" s="2">
+        <f>$OS$2*OS8/(1+$OS$2*OS8)</f>
+        <v>4.9595958072643194E-3</v>
+      </c>
+      <c r="OU8">
+        <v>0.99939999999999996</v>
+      </c>
+      <c r="OW8" s="2">
+        <v>6.6299999999999998E-2</v>
+      </c>
+      <c r="OX8" s="2">
+        <f>$OW$2*OW8/(1+$OW$2*OW8)</f>
+        <v>9.9868026785737661E-3</v>
+      </c>
+      <c r="OY8">
+        <v>0.99880000000000002</v>
+      </c>
+      <c r="PA8" s="2">
+        <v>5.57E-2</v>
+      </c>
+      <c r="PB8" s="2">
+        <f>$PA$2*PA8/(1+$PA$2*PA8)</f>
+        <v>9.9352130117260733E-3</v>
+      </c>
+      <c r="PC8">
+        <v>0.999</v>
+      </c>
     </row>
-    <row r="9" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:419" ht="49" customHeight="1">
       <c r="A9" s="2">
         <v>5</v>
       </c>
@@ -7315,8 +7677,108 @@
         <f t="shared" ref="NO9:NO23" si="102">EXP(-2*NL9*NN9/55.51)</f>
         <v>0.99356430404853902</v>
       </c>
+      <c r="NQ9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="NR9" s="2">
+        <f t="shared" ref="NR9:NR14" si="103">$NQ$2*NQ9/(1+$NQ$2*NQ9)</f>
+        <v>4.4018182774163646E-2</v>
+      </c>
+      <c r="NS9" s="2">
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="NU9" s="2">
+        <v>5.0299999999999997E-3</v>
+      </c>
+      <c r="NV9" s="2">
+        <f t="shared" ref="NV9:NV28" si="104">NU9 * $NU$2/(NU9 * $NU$2+(1-NU9)*$BI$3)</f>
+        <v>8.7638987225568135E-2</v>
+      </c>
+      <c r="NW9" s="2">
+        <v>0.99460000000000004</v>
+      </c>
+      <c r="NY9" s="2">
+        <v>5.0299999999999997E-3</v>
+      </c>
+      <c r="NZ9" s="2">
+        <f t="shared" ref="NZ9:NZ28" si="105">NY9 * $NY$2/(NY9 * $NY$2+(1-NY9)*$BI$3)</f>
+        <v>1.6574878679235946E-2</v>
+      </c>
+      <c r="OA9" s="2">
+        <v>0.995</v>
+      </c>
+      <c r="OC9" s="2">
+        <v>0.95599999999999996</v>
+      </c>
+      <c r="OD9" s="2">
+        <f t="shared" ref="OD9:OD25" si="106">1-OC9</f>
+        <v>4.4000000000000039E-2</v>
+      </c>
+      <c r="OE9" s="2">
+        <v>0.99299999999999999</v>
+      </c>
+      <c r="OG9" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="OH9" s="2">
+        <f t="shared" ref="OH9:OH35" si="107">OG9 * $OG$2/(OG9 * $OG$2+(1-OG9)*$BI$3)</f>
+        <v>7.3295097485502461E-2</v>
+      </c>
+      <c r="OI9" s="2">
+        <v>0.96399999999999997</v>
+      </c>
+      <c r="OK9" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="OL9" s="2">
+        <f t="shared" ref="OL9:OL33" si="108">OK9 * $OG$2/(OK9 * $OG$2+(1-OK9)*$BI$3)</f>
+        <v>0.16141569709968293</v>
+      </c>
+      <c r="OM9" s="2">
+        <v>0.93</v>
+      </c>
+      <c r="OO9" s="2">
+        <v>0.13550000000000001</v>
+      </c>
+      <c r="OP9" s="2">
+        <f t="shared" ref="OP9:OP27" si="109">$OO$2*OO9/(1+$OO$2*OO9)</f>
+        <v>1.9937043401838116E-2</v>
+      </c>
+      <c r="OQ9" s="2">
+        <v>0.99760000000000004</v>
+      </c>
+      <c r="OS9" s="2">
+        <v>6.7199999999999996E-2</v>
+      </c>
+      <c r="OT9" s="2">
+        <f t="shared" ref="OT9:OT25" si="110">$OS$2*OS9/(1+$OS$2*OS9)</f>
+        <v>9.987970007419229E-3</v>
+      </c>
+      <c r="OU9" s="2">
+        <v>0.99880000000000002</v>
+      </c>
+      <c r="OW9" s="2">
+        <v>0.13320000000000001</v>
+      </c>
+      <c r="OX9" s="2">
+        <f t="shared" ref="OX9:OX27" si="111">$OW$2*OW9/(1+$OW$2*OW9)</f>
+        <v>1.9863812429063873E-2</v>
+      </c>
+      <c r="OY9" s="2">
+        <v>0.99760000000000004</v>
+      </c>
+      <c r="PA9" s="2">
+        <v>0.11260000000000001</v>
+      </c>
+      <c r="PB9" s="2">
+        <f t="shared" ref="PB9:PB32" si="112">$PA$2*PA9/(1+$PA$2*PA9)</f>
+        <v>1.9882675722177105E-2</v>
+      </c>
+      <c r="PC9" s="2">
+        <v>0.998</v>
+      </c>
     </row>
-    <row r="10" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:419" ht="49" customHeight="1">
       <c r="P10" s="2">
         <v>3</v>
       </c>
@@ -7615,7 +8077,7 @@
         <v>0.4</v>
       </c>
       <c r="EA10" s="2">
-        <f t="shared" ref="EA10:EA13" si="103">$CF$3*DZ10/(1+$CF$3*DZ10)</f>
+        <f t="shared" ref="EA10:EA13" si="113">$CF$3*DZ10/(1+$CF$3*DZ10)</f>
         <v>4.6729328325484737E-2</v>
       </c>
       <c r="EB10" s="2">
@@ -8308,8 +8770,108 @@
         <f t="shared" si="102"/>
         <v>0.99050117530620008</v>
       </c>
+      <c r="NQ10" s="2">
+        <v>1</v>
+      </c>
+      <c r="NR10" s="2">
+        <f t="shared" si="103"/>
+        <v>8.4324552005787076E-2</v>
+      </c>
+      <c r="NS10" s="2">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="NU10" s="2">
+        <v>9.9226999999999996E-3</v>
+      </c>
+      <c r="NV10" s="2">
+        <f t="shared" si="104"/>
+        <v>0.15996679506743633</v>
+      </c>
+      <c r="NW10" s="2">
+        <v>0.98980000000000001</v>
+      </c>
+      <c r="NY10" s="2">
+        <v>9.92E-3</v>
+      </c>
+      <c r="NZ10" s="2">
+        <f t="shared" si="105"/>
+        <v>3.2323806815488888E-2</v>
+      </c>
+      <c r="OA10" s="2">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="OC10" s="2">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="OD10" s="2">
+        <f t="shared" si="106"/>
+        <v>9.3999999999999972E-2</v>
+      </c>
+      <c r="OE10" s="2">
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="OG10" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="OH10" s="2">
+        <f t="shared" si="107"/>
+        <v>0.11862857437138702</v>
+      </c>
+      <c r="OI10" s="2">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="OK10" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="OL10" s="2">
+        <f t="shared" si="108"/>
+        <v>0.22127230373910331</v>
+      </c>
+      <c r="OM10" s="2">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="OO10" s="2">
+        <v>0.20580000000000001</v>
+      </c>
+      <c r="OP10" s="2">
+        <f t="shared" si="109"/>
+        <v>2.9970754956902306E-2</v>
+      </c>
+      <c r="OQ10" s="2">
+        <v>0.99629999999999996</v>
+      </c>
+      <c r="OS10" s="2">
+        <v>0.1346</v>
+      </c>
+      <c r="OT10" s="2">
+        <f t="shared" si="110"/>
+        <v>1.9807243173192202E-2</v>
+      </c>
+      <c r="OU10" s="2">
+        <v>0.99760000000000004</v>
+      </c>
+      <c r="OW10" s="2">
+        <v>0.2029</v>
+      </c>
+      <c r="OX10" s="2">
+        <f t="shared" si="111"/>
+        <v>2.9946742087531428E-2</v>
+      </c>
+      <c r="OY10" s="2">
+        <v>0.99629999999999996</v>
+      </c>
+      <c r="PA10" s="2">
+        <v>0.16850000000000001</v>
+      </c>
+      <c r="PB10" s="2">
+        <f t="shared" si="112"/>
+        <v>2.9462566060600978E-2</v>
+      </c>
+      <c r="PC10" s="2">
+        <v>0.997</v>
+      </c>
     </row>
-    <row r="11" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:419" ht="49" customHeight="1">
       <c r="A11" s="2">
         <v>6</v>
       </c>
@@ -8623,7 +9185,7 @@
         <v>0.5</v>
       </c>
       <c r="EA11" s="2">
-        <f t="shared" si="103"/>
+        <f t="shared" si="113"/>
         <v>5.7737155779604719E-2</v>
       </c>
       <c r="EB11" s="2">
@@ -9316,8 +9878,108 @@
         <f t="shared" si="102"/>
         <v>0.98749729954970245</v>
       </c>
+      <c r="NQ11" s="2">
+        <v>2</v>
+      </c>
+      <c r="NR11" s="2">
+        <f t="shared" si="103"/>
+        <v>0.15553378709317842</v>
+      </c>
+      <c r="NS11" s="2">
+        <v>0.96699999999999997</v>
+      </c>
+      <c r="NU11" s="2">
+        <v>1.495E-2</v>
+      </c>
+      <c r="NV11" s="2">
+        <f t="shared" si="104"/>
+        <v>0.22382764302456748</v>
+      </c>
+      <c r="NW11" s="2">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="NY11" s="2">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="NZ11" s="2">
+        <f t="shared" si="105"/>
+        <v>4.8316834869212295E-2</v>
+      </c>
+      <c r="OA11" s="2">
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="OC11" s="2">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="OD11" s="2">
+        <f t="shared" si="106"/>
+        <v>0.18200000000000005</v>
+      </c>
+      <c r="OE11" s="2">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="OG11" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="OH11" s="2">
+        <f t="shared" si="107"/>
+        <v>0.16141569709968293</v>
+      </c>
+      <c r="OI11" s="2">
+        <v>0.93100000000000005</v>
+      </c>
+      <c r="OK11" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="OL11" s="2">
+        <f t="shared" si="108"/>
+        <v>0.27647763495313249</v>
+      </c>
+      <c r="OM11" s="2">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="OO11" s="2">
+        <v>0.27839999999999998</v>
+      </c>
+      <c r="OP11" s="2">
+        <f t="shared" si="109"/>
+        <v>4.0119355705995896E-2</v>
+      </c>
+      <c r="OQ11" s="2">
+        <v>0.99509999999999998</v>
+      </c>
+      <c r="OS11" s="2">
+        <v>0.20710000000000001</v>
+      </c>
+      <c r="OT11" s="2">
+        <f t="shared" si="110"/>
+        <v>3.0154365781022607E-2</v>
+      </c>
+      <c r="OU11" s="2">
+        <v>0.99629999999999996</v>
+      </c>
+      <c r="OW11" s="2">
+        <v>0.27179999999999999</v>
+      </c>
+      <c r="OX11" s="2">
+        <f t="shared" si="111"/>
+        <v>3.9712101078521425E-2</v>
+      </c>
+      <c r="OY11" s="2">
+        <v>0.99509999999999998</v>
+      </c>
+      <c r="PA11" s="2">
+        <v>0.22359999999999999</v>
+      </c>
+      <c r="PB11" s="2">
+        <f t="shared" si="112"/>
+        <v>3.8723833755146438E-2</v>
+      </c>
+      <c r="PC11" s="2">
+        <v>0.996</v>
+      </c>
     </row>
-    <row r="12" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:419" ht="49" customHeight="1">
       <c r="A12" s="2">
         <v>7</v>
       </c>
@@ -9618,7 +10280,7 @@
         <v>0.6</v>
       </c>
       <c r="EA12" s="2">
-        <f t="shared" si="103"/>
+        <f t="shared" si="113"/>
         <v>6.8493661099363778E-2</v>
       </c>
       <c r="EB12" s="2">
@@ -10311,8 +10973,108 @@
         <f t="shared" si="102"/>
         <v>0.98453800541176517</v>
       </c>
+      <c r="NQ12" s="2">
+        <v>3</v>
+      </c>
+      <c r="NR12" s="2">
+        <f t="shared" si="103"/>
+        <v>0.21646673509523848</v>
+      </c>
+      <c r="NS12" s="2">
+        <v>0.94699999999999995</v>
+      </c>
+      <c r="NU12" s="2">
+        <v>1.9983999999999998E-2</v>
+      </c>
+      <c r="NV12" s="2">
+        <f t="shared" si="104"/>
+        <v>0.27925619012917413</v>
+      </c>
+      <c r="NW12" s="2">
+        <v>0.97743000000000002</v>
+      </c>
+      <c r="NY12" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="NZ12" s="2">
+        <f t="shared" si="105"/>
+        <v>6.3704198685822486E-2</v>
+      </c>
+      <c r="OA12" s="2">
+        <v>0.98099999999999998</v>
+      </c>
+      <c r="OC12" s="2">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="OD12" s="2">
+        <f t="shared" si="106"/>
+        <v>0.22199999999999998</v>
+      </c>
+      <c r="OE12" s="2">
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="OG12" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="OH12" s="2">
+        <f t="shared" si="107"/>
+        <v>0.20186514572820283</v>
+      </c>
+      <c r="OI12" s="2">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="OK12" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="OL12" s="2">
+        <f t="shared" si="108"/>
+        <v>0.32755356873061442</v>
+      </c>
+      <c r="OM12" s="2">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="OO12" s="2">
+        <v>0.3372</v>
+      </c>
+      <c r="OP12" s="2">
+        <f t="shared" si="109"/>
+        <v>4.8184549279538712E-2</v>
+      </c>
+      <c r="OQ12" s="2">
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="OS12" s="2">
+        <v>0.27660000000000001</v>
+      </c>
+      <c r="OT12" s="2">
+        <f t="shared" si="110"/>
+        <v>3.9870305373608361E-2</v>
+      </c>
+      <c r="OU12" s="2">
+        <v>0.99509999999999998</v>
+      </c>
+      <c r="OW12" s="2">
+        <v>0.34660000000000002</v>
+      </c>
+      <c r="OX12" s="2">
+        <f t="shared" si="111"/>
+        <v>5.0093499771770723E-2</v>
+      </c>
+      <c r="OY12" s="2">
+        <v>0.99380000000000002</v>
+      </c>
+      <c r="PA12" s="2">
+        <v>0.2913</v>
+      </c>
+      <c r="PB12" s="2">
+        <f t="shared" si="112"/>
+        <v>4.986372917571133E-2</v>
+      </c>
+      <c r="PC12" s="2">
+        <v>0.99470000000000003</v>
+      </c>
     </row>
-    <row r="13" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:419" ht="49" customHeight="1">
       <c r="A13" s="2">
         <v>8</v>
       </c>
@@ -10585,7 +11347,7 @@
         <v>0.7</v>
       </c>
       <c r="DQ13" s="2">
-        <f t="shared" ref="DQ13:DQ33" si="104">$CD$3*DP13/(1+$CD$3*DP13)</f>
+        <f t="shared" ref="DQ13:DQ33" si="114">$CD$3*DP13/(1+$CD$3*DP13)</f>
         <v>6.9311187903279087E-2</v>
       </c>
       <c r="DR13" s="2">
@@ -10613,7 +11375,7 @@
         <v>0.7</v>
       </c>
       <c r="EA13" s="2">
-        <f t="shared" si="103"/>
+        <f t="shared" si="113"/>
         <v>7.9007354126277282E-2</v>
       </c>
       <c r="EB13" s="2">
@@ -11265,8 +12027,108 @@
         <f t="shared" si="102"/>
         <v>0.98164416704933211</v>
       </c>
+      <c r="NQ13" s="2">
+        <v>4</v>
+      </c>
+      <c r="NR13" s="2">
+        <f t="shared" si="103"/>
+        <v>0.26919816422578857</v>
+      </c>
+      <c r="NS13" s="2">
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="NU13" s="2">
+        <v>2.487E-2</v>
+      </c>
+      <c r="NV13" s="2">
+        <f t="shared" si="104"/>
+        <v>0.3264191511400994</v>
+      </c>
+      <c r="NW13" s="2">
+        <v>0.9708</v>
+      </c>
+      <c r="NY13" s="2">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="NZ13" s="2">
+        <f t="shared" si="105"/>
+        <v>7.8752237279468174E-2</v>
+      </c>
+      <c r="OA13" s="2">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="OC13" s="2">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="OD13" s="2">
+        <f t="shared" si="106"/>
+        <v>0.29300000000000004</v>
+      </c>
+      <c r="OE13" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="OG13" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="OH13" s="2">
+        <f t="shared" si="107"/>
+        <v>0.25855876080368168</v>
+      </c>
+      <c r="OI13" s="2">
+        <v>0.89800000000000002</v>
+      </c>
+      <c r="OK13" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="OL13" s="2">
+        <f t="shared" si="108"/>
+        <v>0.37494672409398833</v>
+      </c>
+      <c r="OM13" s="2">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="OO13" s="2">
+        <v>0.42370000000000002</v>
+      </c>
+      <c r="OP13" s="2">
+        <f t="shared" si="109"/>
+        <v>5.9805827470339669E-2</v>
+      </c>
+      <c r="OQ13" s="2">
+        <v>0.99250000000000005</v>
+      </c>
+      <c r="OS13" s="2">
+        <v>0.34350000000000003</v>
+      </c>
+      <c r="OT13" s="2">
+        <f t="shared" si="110"/>
+        <v>4.9040645814375464E-2</v>
+      </c>
+      <c r="OU13" s="2">
+        <v>0.99390000000000001</v>
+      </c>
+      <c r="OW13" s="2">
+        <v>0.4199</v>
+      </c>
+      <c r="OX13" s="2">
+        <f t="shared" si="111"/>
+        <v>6.0051244032282979E-2</v>
+      </c>
+      <c r="OY13" s="2">
+        <v>0.99239999999999995</v>
+      </c>
+      <c r="PA13" s="2">
+        <v>0.35389999999999999</v>
+      </c>
+      <c r="PB13" s="2">
+        <f t="shared" si="112"/>
+        <v>5.9937115959870231E-2</v>
+      </c>
+      <c r="PC13" s="2">
+        <v>0.99360000000000004</v>
+      </c>
     </row>
-    <row r="14" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:419" ht="49" customHeight="1">
       <c r="A14" s="2">
         <v>9</v>
       </c>
@@ -11524,7 +12386,7 @@
         <v>0.8</v>
       </c>
       <c r="DQ14" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>7.843614299722057E-2</v>
       </c>
       <c r="DR14" s="2">
@@ -12120,8 +12982,108 @@
         <f t="shared" si="102"/>
         <v>0.97876588737662318</v>
       </c>
+      <c r="NQ14" s="2">
+        <v>5</v>
+      </c>
+      <c r="NR14" s="2">
+        <f t="shared" si="103"/>
+        <v>0.31527953712896711</v>
+      </c>
+      <c r="NS14" s="2">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="NU14" s="2">
+        <v>2.9899999999999999E-2</v>
+      </c>
+      <c r="NV14" s="2">
+        <f t="shared" si="104"/>
+        <v>0.36933799305091281</v>
+      </c>
+      <c r="NW14" s="2">
+        <v>0.96389999999999998</v>
+      </c>
+      <c r="NY14" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="NZ14" s="2">
+        <f t="shared" si="105"/>
+        <v>9.3472052541067177E-2</v>
+      </c>
+      <c r="OA14" s="2">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="OC14" s="2">
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="OD14" s="2">
+        <f t="shared" si="106"/>
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="OE14" s="2">
+        <v>0.94099999999999995</v>
+      </c>
+      <c r="OG14" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="OH14" s="2">
+        <f t="shared" si="107"/>
+        <v>0.29393830294357576</v>
+      </c>
+      <c r="OI14" s="2">
+        <v>0.879</v>
+      </c>
+      <c r="OK14" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="OL14" s="2">
+        <f t="shared" si="108"/>
+        <v>0.4330657010379011</v>
+      </c>
+      <c r="OM14" s="2">
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="OO14" s="2">
+        <v>0.50109999999999999</v>
+      </c>
+      <c r="OP14" s="2">
+        <f t="shared" si="109"/>
+        <v>6.9966549477584711E-2</v>
+      </c>
+      <c r="OQ14" s="2">
+        <v>0.99109999999999998</v>
+      </c>
+      <c r="OS14" s="2">
+        <v>0.41510000000000002</v>
+      </c>
+      <c r="OT14" s="2">
+        <f t="shared" si="110"/>
+        <v>5.8663137127864667E-2</v>
+      </c>
+      <c r="OU14" s="2">
+        <v>0.99260000000000004</v>
+      </c>
+      <c r="OW14" s="2">
+        <v>0.495</v>
+      </c>
+      <c r="OX14" s="2">
+        <f t="shared" si="111"/>
+        <v>7.0039293164765565E-2</v>
+      </c>
+      <c r="OY14" s="2">
+        <v>0.99109999999999998</v>
+      </c>
+      <c r="PA14" s="2">
+        <v>0.40810000000000002</v>
+      </c>
+      <c r="PB14" s="2">
+        <f t="shared" si="112"/>
+        <v>6.8487843975022597E-2</v>
+      </c>
+      <c r="PC14" s="2">
+        <v>0.99260000000000004</v>
+      </c>
     </row>
-    <row r="15" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:419" ht="49" customHeight="1">
       <c r="A15" s="2">
         <v>10</v>
       </c>
@@ -12376,7 +13338,7 @@
         <v>0.9</v>
       </c>
       <c r="DQ15" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>8.7383903824865328E-2</v>
       </c>
       <c r="DR15" s="2">
@@ -12948,8 +13910,98 @@
         <f t="shared" si="102"/>
         <v>0.97593824133000306</v>
       </c>
+      <c r="NU15" s="2">
+        <v>3.4930000000000003E-2</v>
+      </c>
+      <c r="NV15" s="2">
+        <f t="shared" si="104"/>
+        <v>0.40748506990769284</v>
+      </c>
+      <c r="NW15" s="2">
+        <v>0.95640000000000003</v>
+      </c>
+      <c r="NY15" s="2">
+        <v>3.49E-2</v>
+      </c>
+      <c r="NZ15" s="2">
+        <f t="shared" si="105"/>
+        <v>0.10758926897525126</v>
+      </c>
+      <c r="OA15" s="2">
+        <v>0.96699999999999997</v>
+      </c>
+      <c r="OC15" s="2">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="OD15" s="2">
+        <f t="shared" si="106"/>
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="OE15" s="2">
+        <v>0.92700000000000005</v>
+      </c>
+      <c r="OG15" s="2">
+        <v>0.17</v>
+      </c>
+      <c r="OH15" s="2">
+        <f t="shared" si="107"/>
+        <v>0.34374033053389719</v>
+      </c>
+      <c r="OI15" s="2">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="OK15" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="OL15" s="2">
+        <f t="shared" si="108"/>
+        <v>0.48608725725238722</v>
+      </c>
+      <c r="OM15" s="2">
+        <v>0.76300000000000001</v>
+      </c>
+      <c r="OO15" s="2">
+        <v>0.58009999999999995</v>
+      </c>
+      <c r="OP15" s="2">
+        <f t="shared" si="109"/>
+        <v>8.0113311605480964E-2</v>
+      </c>
+      <c r="OQ15" s="2">
+        <v>0.98980000000000001</v>
+      </c>
+      <c r="OS15" s="2">
+        <v>0.49519999999999997</v>
+      </c>
+      <c r="OT15" s="2">
+        <f t="shared" si="110"/>
+        <v>6.9199762814228197E-2</v>
+      </c>
+      <c r="OU15" s="2">
+        <v>0.99119999999999997</v>
+      </c>
+      <c r="OW15" s="2">
+        <v>0.56430000000000002</v>
+      </c>
+      <c r="OX15" s="2">
+        <f t="shared" si="111"/>
+        <v>7.9069478355344627E-2</v>
+      </c>
+      <c r="OY15" s="2">
+        <v>0.98980000000000001</v>
+      </c>
+      <c r="PA15" s="2">
+        <v>0.47749999999999998</v>
+      </c>
+      <c r="PB15" s="2">
+        <f t="shared" si="112"/>
+        <v>7.9212070719459488E-2</v>
+      </c>
+      <c r="PC15" s="2">
+        <v>0.99139999999999995</v>
+      </c>
     </row>
-    <row r="16" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:419" ht="49" customHeight="1">
       <c r="A16" s="2">
         <v>11</v>
       </c>
@@ -13191,7 +14243,7 @@
         <v>1</v>
       </c>
       <c r="DQ16" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>9.6159582064190743E-2</v>
       </c>
       <c r="DR16" s="2">
@@ -13679,8 +14731,98 @@
         <f t="shared" si="102"/>
         <v>0.97316083846816936</v>
       </c>
+      <c r="NU16" s="2">
+        <v>3.9960000000000002E-2</v>
+      </c>
+      <c r="NV16" s="2">
+        <f t="shared" si="104"/>
+        <v>0.44161426804393239</v>
+      </c>
+      <c r="NW16" s="2">
+        <v>0.9486</v>
+      </c>
+      <c r="NY16" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="NZ16" s="2">
+        <f t="shared" si="105"/>
+        <v>0.12196905081028393</v>
+      </c>
+      <c r="OA16" s="2">
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="OC16" s="2">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="OD16" s="2">
+        <f t="shared" si="106"/>
+        <v>0.44899999999999995</v>
+      </c>
+      <c r="OE16" s="2">
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="OG16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="OH16" s="2">
+        <f t="shared" si="107"/>
+        <v>0.3899940743248963</v>
+      </c>
+      <c r="OI16" s="2">
+        <v>0.85099999999999998</v>
+      </c>
+      <c r="OK16" s="2">
+        <v>0.31</v>
+      </c>
+      <c r="OL16" s="2">
+        <f t="shared" si="108"/>
+        <v>0.53465383600285266</v>
+      </c>
+      <c r="OM16" s="2">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="OO16" s="2">
+        <v>0.65580000000000005</v>
+      </c>
+      <c r="OP16" s="2">
+        <f t="shared" si="109"/>
+        <v>8.9630645983509477E-2</v>
+      </c>
+      <c r="OQ16" s="2">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="OS16" s="2">
+        <v>0.57850000000000001</v>
+      </c>
+      <c r="OT16" s="2">
+        <f t="shared" si="110"/>
+        <v>7.9910004709434643E-2</v>
+      </c>
+      <c r="OU16" s="2">
+        <v>0.98970000000000002</v>
+      </c>
+      <c r="OW16" s="2">
+        <v>0.63429999999999997</v>
+      </c>
+      <c r="OX16" s="2">
+        <f t="shared" si="111"/>
+        <v>8.8014569368527931E-2</v>
+      </c>
+      <c r="OY16" s="2">
+        <v>0.98860000000000003</v>
+      </c>
+      <c r="PA16" s="2">
+        <v>0.53820000000000001</v>
+      </c>
+      <c r="PB16" s="2">
+        <f t="shared" si="112"/>
+        <v>8.8391486760848126E-2</v>
+      </c>
+      <c r="PC16" s="2">
+        <v>0.99029999999999996</v>
+      </c>
     </row>
-    <row r="17" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:419" ht="49" customHeight="1">
       <c r="A17" s="2">
         <v>12</v>
       </c>
@@ -13925,7 +15067,7 @@
         <v>1.2</v>
       </c>
       <c r="DQ17" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.11321417296580201</v>
       </c>
       <c r="DR17" s="2">
@@ -14385,8 +15527,98 @@
         <f t="shared" si="102"/>
         <v>0.97043329597707373</v>
       </c>
+      <c r="NU17" s="2">
+        <v>4.4850000000000001E-2</v>
+      </c>
+      <c r="NV17" s="2">
+        <f t="shared" si="104"/>
+        <v>0.47151537413074923</v>
+      </c>
+      <c r="NW17" s="2">
+        <v>0.94079999999999997</v>
+      </c>
+      <c r="NY17" s="2">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="NZ17" s="2">
+        <f t="shared" si="105"/>
+        <v>0.13576614285660465</v>
+      </c>
+      <c r="OA17" s="2">
+        <v>0.95699999999999996</v>
+      </c>
+      <c r="OC17" s="2">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="OD17" s="2">
+        <f t="shared" si="106"/>
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="OE17" s="2">
+        <v>0.89</v>
+      </c>
+      <c r="OG17" s="2">
+        <v>0.24</v>
+      </c>
+      <c r="OH17" s="2">
+        <f t="shared" si="107"/>
+        <v>0.44677188644022603</v>
+      </c>
+      <c r="OI17" s="2">
+        <v>0.84099999999999997</v>
+      </c>
+      <c r="OK17" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="OL17" s="2">
+        <f t="shared" si="108"/>
+        <v>0.57930427441012422</v>
+      </c>
+      <c r="OM17" s="2">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="OO17" s="2">
+        <v>0.73929999999999996</v>
+      </c>
+      <c r="OP17" s="2">
+        <f t="shared" si="109"/>
+        <v>9.9902787790896688E-2</v>
+      </c>
+      <c r="OQ17" s="2">
+        <v>0.98699999999999999</v>
+      </c>
+      <c r="OS17" s="2">
+        <v>0.64980000000000004</v>
+      </c>
+      <c r="OT17" s="2">
+        <f t="shared" si="110"/>
+        <v>8.8883491718152297E-2</v>
+      </c>
+      <c r="OU17" s="2">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="OW17" s="2">
+        <v>0.72960000000000003</v>
+      </c>
+      <c r="OX17" s="2">
+        <f t="shared" si="111"/>
+        <v>9.9916990744554415E-2</v>
+      </c>
+      <c r="OY17" s="2">
+        <v>0.9869</v>
+      </c>
+      <c r="PA17" s="2">
+        <v>0.57079999999999997</v>
+      </c>
+      <c r="PB17" s="2">
+        <f t="shared" si="112"/>
+        <v>9.3246312834838738E-2</v>
+      </c>
+      <c r="PC17" s="2">
+        <v>0.98970000000000002</v>
+      </c>
     </row>
-    <row r="18" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:419" ht="49" customHeight="1">
       <c r="W18" s="2">
         <v>5</v>
       </c>
@@ -14606,7 +15838,7 @@
         <v>1.4</v>
       </c>
       <c r="DQ18" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.12963707606797881</v>
       </c>
       <c r="DR18" s="2">
@@ -15024,8 +16256,98 @@
         <f t="shared" si="102"/>
         <v>0.96500112356194612</v>
       </c>
+      <c r="NU18" s="2">
+        <v>4.9880000000000001E-2</v>
+      </c>
+      <c r="NV18" s="2">
+        <f t="shared" si="104"/>
+        <v>0.49937865775509582</v>
+      </c>
+      <c r="NW18" s="2">
+        <v>0.93240000000000001</v>
+      </c>
+      <c r="NY18" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="NZ18" s="2">
+        <f t="shared" si="105"/>
+        <v>0.14927487603922013</v>
+      </c>
+      <c r="OA18" s="2">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="OC18" s="2">
+        <v>0.41</v>
+      </c>
+      <c r="OD18" s="2">
+        <f t="shared" si="106"/>
+        <v>0.59000000000000008</v>
+      </c>
+      <c r="OE18" s="2">
+        <v>0.84399999999999997</v>
+      </c>
+      <c r="OG18" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="OH18" s="2">
+        <f t="shared" si="107"/>
+        <v>0.48608725725238722</v>
+      </c>
+      <c r="OI18" s="2">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="OK18" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="OL18" s="2">
+        <f t="shared" si="108"/>
+        <v>0.63029722611759076</v>
+      </c>
+      <c r="OM18" s="2">
+        <v>0.66100000000000003</v>
+      </c>
+      <c r="OO18" s="2">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="OP18" s="2">
+        <f t="shared" si="109"/>
+        <v>0.10913622846479369</v>
+      </c>
+      <c r="OQ18" s="2">
+        <v>0.98560000000000003</v>
+      </c>
+      <c r="OS18" s="2">
+        <v>0.82040000000000002</v>
+      </c>
+      <c r="OT18" s="2">
+        <f t="shared" si="110"/>
+        <v>0.10966017534502082</v>
+      </c>
+      <c r="OU18" s="2">
+        <v>0.98540000000000005</v>
+      </c>
+      <c r="OW18" s="2">
+        <v>0.79200000000000004</v>
+      </c>
+      <c r="OX18" s="2">
+        <f t="shared" si="111"/>
+        <v>0.10754350636160839</v>
+      </c>
+      <c r="OY18" s="2">
+        <v>0.98570000000000002</v>
+      </c>
+      <c r="PA18" s="2">
+        <v>0.62090000000000001</v>
+      </c>
+      <c r="PB18" s="2">
+        <f t="shared" si="112"/>
+        <v>0.10060727859965962</v>
+      </c>
+      <c r="PC18" s="2">
+        <v>0.98880000000000001</v>
+      </c>
     </row>
-    <row r="19" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:419" ht="49" customHeight="1">
       <c r="A19" s="2">
         <v>13</v>
       </c>
@@ -15240,7 +16562,7 @@
         <v>1.6</v>
       </c>
       <c r="DQ19" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.14546274901215495</v>
       </c>
       <c r="DR19" s="2">
@@ -15657,8 +16979,98 @@
         <f t="shared" si="102"/>
         <v>0.95972383290643648</v>
       </c>
+      <c r="NU19" s="2">
+        <v>5.491E-2</v>
+      </c>
+      <c r="NV19" s="2">
+        <f t="shared" si="104"/>
+        <v>0.52470439786446232</v>
+      </c>
+      <c r="NW19" s="2">
+        <v>0.92400000000000004</v>
+      </c>
+      <c r="NY19" s="2">
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="NZ19" s="2">
+        <f t="shared" si="105"/>
+        <v>0.162242292646747</v>
+      </c>
+      <c r="OA19" s="2">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="OC19" s="2">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="OD19" s="2">
+        <f t="shared" si="106"/>
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="OE19" s="2">
+        <v>0.77700000000000002</v>
+      </c>
+      <c r="OG19" s="2">
+        <v>0.32</v>
+      </c>
+      <c r="OH19" s="2">
+        <f t="shared" si="107"/>
+        <v>0.54616450434563557</v>
+      </c>
+      <c r="OI19" s="2">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="OK19" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="OL19" s="2">
+        <f t="shared" si="108"/>
+        <v>0.67662105598120093</v>
+      </c>
+      <c r="OM19" s="2">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="OO19" s="2">
+        <v>0.90590000000000004</v>
+      </c>
+      <c r="OP19" s="2">
+        <f t="shared" si="109"/>
+        <v>0.11972045399076039</v>
+      </c>
+      <c r="OQ19" s="2">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="OS19" s="2">
+        <v>0.90549999999999997</v>
+      </c>
+      <c r="OT19" s="2">
+        <f t="shared" si="110"/>
+        <v>0.11967391771159867</v>
+      </c>
+      <c r="OU19" s="2">
+        <v>0.9839</v>
+      </c>
+      <c r="OW19" s="2">
+        <v>0.89080000000000004</v>
+      </c>
+      <c r="OX19" s="2">
+        <f t="shared" si="111"/>
+        <v>0.11935800635052078</v>
+      </c>
+      <c r="OY19" s="2">
+        <v>0.9839</v>
+      </c>
+      <c r="PA19" s="2">
+        <v>0.68149999999999999</v>
+      </c>
+      <c r="PB19" s="2">
+        <f t="shared" si="112"/>
+        <v>0.10935280729857585</v>
+      </c>
+      <c r="PC19" s="2">
+        <v>0.98770000000000002</v>
+      </c>
     </row>
-    <row r="20" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:419" ht="49" customHeight="1">
       <c r="A20" s="2">
         <v>14</v>
       </c>
@@ -15851,7 +17263,7 @@
         <v>1.8</v>
       </c>
       <c r="DQ20" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.16072318804332683</v>
       </c>
       <c r="DR20" s="2">
@@ -16268,8 +17680,98 @@
         <f t="shared" si="102"/>
         <v>0.9544891579348479</v>
       </c>
+      <c r="NU20" s="2">
+        <v>5.994E-2</v>
+      </c>
+      <c r="NV20" s="2">
+        <f t="shared" si="104"/>
+        <v>0.54782414300593996</v>
+      </c>
+      <c r="NW20" s="2">
+        <v>0.91500000000000004</v>
+      </c>
+      <c r="NY20" s="2">
+        <v>6.0100000000000001E-2</v>
+      </c>
+      <c r="NZ20" s="2">
+        <f t="shared" si="105"/>
+        <v>0.17571915009146305</v>
+      </c>
+      <c r="OA20" s="2">
+        <v>0.94399999999999995</v>
+      </c>
+      <c r="OC20" s="2">
+        <v>0.24</v>
+      </c>
+      <c r="OD20" s="2">
+        <f t="shared" si="106"/>
+        <v>0.76</v>
+      </c>
+      <c r="OE20" s="2">
+        <v>0.72599999999999998</v>
+      </c>
+      <c r="OG20" s="2">
+        <v>0.36</v>
+      </c>
+      <c r="OH20" s="2">
+        <f t="shared" si="107"/>
+        <v>0.58990994067181701</v>
+      </c>
+      <c r="OI20" s="2">
+        <v>0.79400000000000004</v>
+      </c>
+      <c r="OK20" s="2">
+        <v>0.51</v>
+      </c>
+      <c r="OL20" s="2">
+        <f t="shared" si="108"/>
+        <v>0.72690231893339274</v>
+      </c>
+      <c r="OM20" s="2">
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="OO20" s="2">
+        <v>1.0226999999999999</v>
+      </c>
+      <c r="OP20" s="2">
+        <f t="shared" si="109"/>
+        <v>0.13310177690027294</v>
+      </c>
+      <c r="OQ20" s="2">
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="OS20" s="2">
+        <v>1.0410999999999999</v>
+      </c>
+      <c r="OT20" s="2">
+        <f t="shared" si="110"/>
+        <v>0.13517278961838031</v>
+      </c>
+      <c r="OU20" s="2">
+        <v>0.98150000000000004</v>
+      </c>
+      <c r="OW20" s="2">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="OX20" s="2">
+        <f t="shared" si="111"/>
+        <v>0.13204599581636622</v>
+      </c>
+      <c r="OY20" s="2">
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="PA20" s="2">
+        <v>0.73470000000000002</v>
+      </c>
+      <c r="PB20" s="2">
+        <f t="shared" si="112"/>
+        <v>0.11689139213834393</v>
+      </c>
+      <c r="PC20" s="2">
+        <v>0.98670000000000002</v>
+      </c>
     </row>
-    <row r="21" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:419" ht="49" customHeight="1">
       <c r="A21" s="2">
         <v>15</v>
       </c>
@@ -16396,7 +17898,7 @@
         <v>2</v>
       </c>
       <c r="DQ21" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.17544814393377201</v>
       </c>
       <c r="DR21" s="2">
@@ -16813,8 +18315,98 @@
         <f t="shared" si="102"/>
         <v>0.94919411309530544</v>
       </c>
+      <c r="NU21" s="2">
+        <v>6.497E-2</v>
+      </c>
+      <c r="NV21" s="2">
+        <f t="shared" si="104"/>
+        <v>0.56901409330720221</v>
+      </c>
+      <c r="NW21" s="2">
+        <v>0.90629999999999999</v>
+      </c>
+      <c r="NY21" s="2">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="NZ21" s="2">
+        <f t="shared" si="105"/>
+        <v>0.18815857489363394</v>
+      </c>
+      <c r="OA21" s="2">
+        <v>0.93899999999999995</v>
+      </c>
+      <c r="OC21" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="OD21" s="2">
+        <f t="shared" si="106"/>
+        <v>0.86</v>
+      </c>
+      <c r="OE21" s="2">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="OG21" s="2">
+        <v>0.42</v>
+      </c>
+      <c r="OH21" s="2">
+        <f t="shared" si="107"/>
+        <v>0.64935012635033773</v>
+      </c>
+      <c r="OI21" s="2">
+        <v>0.76700000000000002</v>
+      </c>
+      <c r="OK21" s="2">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="OL21" s="2">
+        <f t="shared" si="108"/>
+        <v>0.7722057792147643</v>
+      </c>
+      <c r="OM21" s="2">
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="OO21" s="2">
+        <v>1.1649</v>
+      </c>
+      <c r="OP21" s="2">
+        <f t="shared" si="109"/>
+        <v>0.14885390748620922</v>
+      </c>
+      <c r="OQ21" s="2">
+        <v>0.97950000000000004</v>
+      </c>
+      <c r="OS21" s="2">
+        <v>1.177</v>
+      </c>
+      <c r="OT21" s="2">
+        <f t="shared" si="110"/>
+        <v>0.15016789155659591</v>
+      </c>
+      <c r="OU21" s="2">
+        <v>0.97909999999999997</v>
+      </c>
+      <c r="OW21" s="2">
+        <v>1.1429</v>
+      </c>
+      <c r="OX21" s="2">
+        <f t="shared" si="111"/>
+        <v>0.14813304817541451</v>
+      </c>
+      <c r="OY21" s="2">
+        <v>0.97940000000000005</v>
+      </c>
+      <c r="PA21" s="2">
+        <v>0.79630000000000001</v>
+      </c>
+      <c r="PB21" s="2">
+        <f t="shared" si="112"/>
+        <v>0.12546239601642942</v>
+      </c>
+      <c r="PC21" s="2">
+        <v>0.98560000000000003</v>
+      </c>
     </row>
-    <row r="22" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:419" ht="49" customHeight="1">
       <c r="A22" s="2">
         <v>16</v>
       </c>
@@ -16951,7 +18543,7 @@
         <v>2.4</v>
       </c>
       <c r="DQ22" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.20340052384381552</v>
       </c>
       <c r="DR22" s="2">
@@ -17368,8 +18960,98 @@
         <f t="shared" si="102"/>
         <v>0.94398285907405555</v>
       </c>
+      <c r="NU22" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="NV22" s="2">
+        <f t="shared" si="104"/>
+        <v>0.58850618753062456</v>
+      </c>
+      <c r="NW22" s="2">
+        <v>0.89670000000000005</v>
+      </c>
+      <c r="NY22" s="2">
+        <v>6.9900000000000004E-2</v>
+      </c>
+      <c r="NZ22" s="2">
+        <f t="shared" si="105"/>
+        <v>0.20035338929367744</v>
+      </c>
+      <c r="OA22" s="2">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="OC22" s="2">
+        <v>0.121</v>
+      </c>
+      <c r="OD22" s="2">
+        <f t="shared" si="106"/>
+        <v>0.879</v>
+      </c>
+      <c r="OE22" s="2">
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="OG22" s="2">
+        <v>0.48</v>
+      </c>
+      <c r="OH22" s="2">
+        <f t="shared" si="107"/>
+        <v>0.70243381806399974</v>
+      </c>
+      <c r="OI22" s="2">
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="OK22" s="2">
+        <v>0.64</v>
+      </c>
+      <c r="OL22" s="2">
+        <f t="shared" si="108"/>
+        <v>0.8197007522893951</v>
+      </c>
+      <c r="OM22" s="2">
+        <v>0.46400000000000002</v>
+      </c>
+      <c r="OO22" s="2">
+        <v>1.3063</v>
+      </c>
+      <c r="OP22" s="2">
+        <f t="shared" si="109"/>
+        <v>0.1639598606126792</v>
+      </c>
+      <c r="OQ22" s="2">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="OS22" s="2">
+        <v>1.3128</v>
+      </c>
+      <c r="OT22" s="2">
+        <f t="shared" si="110"/>
+        <v>0.16464138425525299</v>
+      </c>
+      <c r="OU22" s="2">
+        <v>0.9768</v>
+      </c>
+      <c r="OW22" s="2">
+        <v>1.2974000000000001</v>
+      </c>
+      <c r="OX22" s="2">
+        <f t="shared" si="111"/>
+        <v>0.1648567790759142</v>
+      </c>
+      <c r="OY22" s="2">
+        <v>0.97660000000000002</v>
+      </c>
+      <c r="PA22" s="2">
+        <v>0.90849999999999997</v>
+      </c>
+      <c r="PB22" s="2">
+        <f t="shared" si="112"/>
+        <v>0.14065379883956639</v>
+      </c>
+      <c r="PC22" s="2">
+        <v>0.98360000000000003</v>
+      </c>
     </row>
-    <row r="23" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:419" ht="49" customHeight="1">
       <c r="A23" s="2">
         <v>17</v>
       </c>
@@ -17499,7 +19181,7 @@
         <v>2.7</v>
       </c>
       <c r="DQ23" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.22315193672106418</v>
       </c>
       <c r="DR23" s="2">
@@ -17916,8 +19598,98 @@
         <f t="shared" si="102"/>
         <v>0.93114664790012913</v>
       </c>
+      <c r="NU23" s="2">
+        <v>7.5029999999999999E-2</v>
+      </c>
+      <c r="NV23" s="2">
+        <f t="shared" si="104"/>
+        <v>0.60649662771629431</v>
+      </c>
+      <c r="NW23" s="2">
+        <v>0.8871</v>
+      </c>
+      <c r="NY23" s="2">
+        <v>7.51E-2</v>
+      </c>
+      <c r="NZ23" s="2">
+        <f t="shared" si="105"/>
+        <v>0.21303526100823</v>
+      </c>
+      <c r="OA23" s="2">
+        <v>0.93</v>
+      </c>
+      <c r="OC23" s="2">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="OD23" s="2">
+        <f t="shared" si="106"/>
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="OE23" s="2">
+        <v>0.441</v>
+      </c>
+      <c r="OG23" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="OH23" s="2">
+        <f t="shared" si="107"/>
+        <v>0.75761131999312314</v>
+      </c>
+      <c r="OI23" s="2">
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="OK23" s="2">
+        <v>0.72</v>
+      </c>
+      <c r="OL23" s="2">
+        <f t="shared" si="108"/>
+        <v>0.86800332857075568</v>
+      </c>
+      <c r="OM23" s="2">
+        <v>0.495</v>
+      </c>
+      <c r="OO23" s="2">
+        <v>1.6615</v>
+      </c>
+      <c r="OP23" s="2">
+        <f t="shared" si="109"/>
+        <v>0.19964207673528431</v>
+      </c>
+      <c r="OQ23" s="2">
+        <v>0.97070000000000001</v>
+      </c>
+      <c r="OS23" s="2">
+        <v>1.6594</v>
+      </c>
+      <c r="OT23" s="2">
+        <f t="shared" si="110"/>
+        <v>0.19944007045273218</v>
+      </c>
+      <c r="OU23" s="2">
+        <v>0.97070000000000001</v>
+      </c>
+      <c r="OW23" s="2">
+        <v>1.4741</v>
+      </c>
+      <c r="OX23" s="2">
+        <f t="shared" si="111"/>
+        <v>0.18319626597519548</v>
+      </c>
+      <c r="OY23" s="2">
+        <v>0.97340000000000004</v>
+      </c>
+      <c r="PA23" s="2">
+        <v>1.0193000000000001</v>
+      </c>
+      <c r="PB23" s="2">
+        <f t="shared" si="112"/>
+        <v>0.15514644637427921</v>
+      </c>
+      <c r="PC23" s="2">
+        <v>0.98160000000000003</v>
+      </c>
     </row>
-    <row r="24" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:419" ht="49" customHeight="1">
       <c r="A24" s="2">
         <v>18</v>
       </c>
@@ -17979,7 +19751,7 @@
         <v>3</v>
       </c>
       <c r="DQ24" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.24194758825625207</v>
       </c>
       <c r="DR24" s="2">
@@ -18368,8 +20140,98 @@
         <f t="shared" si="100"/>
         <v>0.90916736177303581</v>
       </c>
+      <c r="NU24" s="2">
+        <v>8.0049999999999996E-2</v>
+      </c>
+      <c r="NV24" s="2">
+        <f t="shared" si="104"/>
+        <v>0.62312061946903097</v>
+      </c>
+      <c r="NW24" s="2">
+        <v>0.87749999999999995</v>
+      </c>
+      <c r="NY24" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="NZ24" s="2">
+        <f t="shared" si="105"/>
+        <v>0.22474811259857991</v>
+      </c>
+      <c r="OA24" s="2">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="OC24" s="2">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="OD24" s="2">
+        <f t="shared" si="106"/>
+        <v>0.92600000000000005</v>
+      </c>
+      <c r="OE24" s="2">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="OG24" s="2">
+        <v>0.64</v>
+      </c>
+      <c r="OH24" s="2">
+        <f t="shared" si="107"/>
+        <v>0.8197007522893951</v>
+      </c>
+      <c r="OI24" s="2">
+        <v>0.64700000000000002</v>
+      </c>
+      <c r="OK24" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="OL24" s="2">
+        <f t="shared" si="108"/>
+        <v>0.91094688450035832</v>
+      </c>
+      <c r="OM24" s="2">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="OO24" s="2">
+        <v>1.9876</v>
+      </c>
+      <c r="OP24" s="2">
+        <f t="shared" si="109"/>
+        <v>0.22982036234629089</v>
+      </c>
+      <c r="OQ24" s="2">
+        <v>0.96509999999999996</v>
+      </c>
+      <c r="OS24" s="2">
+        <v>2.4020000000000001</v>
+      </c>
+      <c r="OT24" s="2">
+        <f t="shared" si="110"/>
+        <v>0.26503675632027596</v>
+      </c>
+      <c r="OU24" s="2">
+        <v>0.95760000000000001</v>
+      </c>
+      <c r="OW24" s="2">
+        <v>2.0274000000000001</v>
+      </c>
+      <c r="OX24" s="2">
+        <f t="shared" si="111"/>
+        <v>0.2357479857889784</v>
+      </c>
+      <c r="OY24" s="2">
+        <v>0.96319999999999995</v>
+      </c>
+      <c r="PA24" s="2">
+        <v>1.1093</v>
+      </c>
+      <c r="PB24" s="2">
+        <f t="shared" si="112"/>
+        <v>0.16656352056797213</v>
+      </c>
+      <c r="PC24" s="2">
+        <v>0.97989999999999999</v>
+      </c>
     </row>
-    <row r="25" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:419" ht="49" customHeight="1">
       <c r="A25" s="2">
         <v>19</v>
       </c>
@@ -18421,7 +20283,7 @@
         <v>3.4</v>
       </c>
       <c r="DQ25" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.26563787428601643</v>
       </c>
       <c r="DR25" s="2">
@@ -18782,8 +20644,98 @@
         <f t="shared" si="100"/>
         <v>0.89428781344293951</v>
       </c>
+      <c r="NU25" s="2">
+        <v>8.5080000000000003E-2</v>
+      </c>
+      <c r="NV25" s="2">
+        <f t="shared" si="104"/>
+        <v>0.63858736640806757</v>
+      </c>
+      <c r="NW25" s="2">
+        <v>0.86729999999999996</v>
+      </c>
+      <c r="NY25" s="2">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="NZ25" s="2">
+        <f t="shared" si="105"/>
+        <v>0.23646956237775793</v>
+      </c>
+      <c r="OA25" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="OC25" s="2">
+        <v>6.3E-2</v>
+      </c>
+      <c r="OD25" s="2">
+        <f t="shared" si="106"/>
+        <v>0.93700000000000006</v>
+      </c>
+      <c r="OE25" s="2">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="OG25" s="2">
+        <v>0.74</v>
+      </c>
+      <c r="OH25" s="2">
+        <f t="shared" si="107"/>
+        <v>0.8792052754689148</v>
+      </c>
+      <c r="OI25" s="2">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="OK25" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="OL25" s="2">
+        <f t="shared" si="108"/>
+        <v>0.92094851060821403</v>
+      </c>
+      <c r="OM25" s="2">
+        <v>0.253</v>
+      </c>
+      <c r="OO25" s="2">
+        <v>2.3380000000000001</v>
+      </c>
+      <c r="OP25" s="2">
+        <f t="shared" si="109"/>
+        <v>0.25980970862305552</v>
+      </c>
+      <c r="OQ25" s="2">
+        <v>0.95889999999999997</v>
+      </c>
+      <c r="OS25" s="2">
+        <v>3.2715999999999998</v>
+      </c>
+      <c r="OT25" s="2">
+        <f t="shared" si="110"/>
+        <v>0.32938354008434323</v>
+      </c>
+      <c r="OU25" s="2">
+        <v>0.94189999999999996</v>
+      </c>
+      <c r="OW25" s="2">
+        <v>2.6463000000000001</v>
+      </c>
+      <c r="OX25" s="2">
+        <f t="shared" si="111"/>
+        <v>0.28705591662153168</v>
+      </c>
+      <c r="OY25" s="2">
+        <v>0.95179999999999998</v>
+      </c>
+      <c r="PA25" s="2">
+        <v>1.2150000000000001</v>
+      </c>
+      <c r="PB25" s="2">
+        <f t="shared" si="112"/>
+        <v>0.17958438401226554</v>
+      </c>
+      <c r="PC25" s="2">
+        <v>0.97799999999999998</v>
+      </c>
     </row>
-    <row r="26" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:419" ht="49" customHeight="1">
       <c r="A26" s="2">
         <v>20</v>
       </c>
@@ -18822,7 +20774,7 @@
         <v>3.7</v>
       </c>
       <c r="DQ26" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.28245612398584147</v>
       </c>
       <c r="DR26" s="2">
@@ -19169,8 +21121,78 @@
         <f t="shared" si="94"/>
         <v>0.79155201649387652</v>
       </c>
+      <c r="NU26" s="2">
+        <v>9.0109999999999996E-2</v>
+      </c>
+      <c r="NV26" s="2">
+        <f t="shared" si="104"/>
+        <v>0.65298592520477883</v>
+      </c>
+      <c r="NW26" s="2">
+        <v>0.85680000000000001</v>
+      </c>
+      <c r="NY26" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="NZ26" s="2">
+        <f t="shared" si="105"/>
+        <v>0.247964934251722</v>
+      </c>
+      <c r="OA26" s="2">
+        <v>0.91600000000000004</v>
+      </c>
+      <c r="OG26" s="2">
+        <v>0.76</v>
+      </c>
+      <c r="OH26" s="2">
+        <f t="shared" si="107"/>
+        <v>0.89008765329157435</v>
+      </c>
+      <c r="OI26" s="2">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="OK26" s="2">
+        <v>0.84</v>
+      </c>
+      <c r="OL26" s="2">
+        <f t="shared" si="108"/>
+        <v>0.93068021124931455</v>
+      </c>
+      <c r="OM26" s="2">
+        <v>0.315</v>
+      </c>
+      <c r="OO26" s="2">
+        <v>2.722</v>
+      </c>
+      <c r="OP26" s="2">
+        <f t="shared" si="109"/>
+        <v>0.29010239605633137</v>
+      </c>
+      <c r="OQ26" s="2">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="OW26" s="2">
+        <v>3.2894999999999999</v>
+      </c>
+      <c r="OX26" s="2">
+        <f t="shared" si="111"/>
+        <v>0.33355433782233918</v>
+      </c>
+      <c r="OY26" s="2">
+        <v>0.94010000000000005</v>
+      </c>
+      <c r="PA26" s="2">
+        <v>1.3226</v>
+      </c>
+      <c r="PB26" s="2">
+        <f t="shared" si="112"/>
+        <v>0.19242795643338764</v>
+      </c>
+      <c r="PC26" s="2">
+        <v>0.97609999999999997</v>
+      </c>
     </row>
-    <row r="27" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:419" ht="49" customHeight="1">
       <c r="DS27"/>
       <c r="DX27"/>
       <c r="KT27" s="2">
@@ -19229,8 +21251,78 @@
         <f t="shared" si="94"/>
         <v>0.75443431260423632</v>
       </c>
+      <c r="NU27" s="2">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="NV27" s="2">
+        <f t="shared" si="104"/>
+        <v>0.6660614076726562</v>
+      </c>
+      <c r="NW27" s="2">
+        <v>0.84660000000000002</v>
+      </c>
+      <c r="NY27" s="2">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="NZ27" s="2">
+        <f t="shared" si="105"/>
+        <v>0.2592407064748839</v>
+      </c>
+      <c r="OA27" s="2">
+        <v>0.91100000000000003</v>
+      </c>
+      <c r="OG27" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="OH27" s="2">
+        <f t="shared" si="107"/>
+        <v>0.9006639447188951</v>
+      </c>
+      <c r="OI27" s="2">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="OK27" s="2">
+        <v>0.86</v>
+      </c>
+      <c r="OL27" s="2">
+        <f t="shared" si="108"/>
+        <v>0.9401527681213413</v>
+      </c>
+      <c r="OM27" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="OO27" s="2">
+        <v>2.9983</v>
+      </c>
+      <c r="OP27" s="2">
+        <f t="shared" si="109"/>
+        <v>0.31040892578992479</v>
+      </c>
+      <c r="OQ27" s="2">
+        <v>0.94699999999999995</v>
+      </c>
+      <c r="OW27" s="2">
+        <v>4.4126000000000003</v>
+      </c>
+      <c r="OX27" s="2">
+        <f t="shared" si="111"/>
+        <v>0.40169097328000358</v>
+      </c>
+      <c r="OY27" s="2">
+        <v>0.92010000000000003</v>
+      </c>
+      <c r="PA27" s="2">
+        <v>1.5688</v>
+      </c>
+      <c r="PB27" s="2">
+        <f t="shared" si="112"/>
+        <v>0.22035497724384578</v>
+      </c>
+      <c r="PC27" s="2">
+        <v>0.97150000000000003</v>
+      </c>
     </row>
-    <row r="28" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:419" ht="49" customHeight="1">
       <c r="A28" s="2">
         <v>22</v>
       </c>
@@ -19269,7 +21361,7 @@
         <v>4</v>
       </c>
       <c r="DQ28" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.29852128286427793</v>
       </c>
       <c r="DR28" s="2">
@@ -19616,8 +21708,58 @@
         <f t="shared" si="94"/>
         <v>0.71528460874328337</v>
       </c>
+      <c r="NU28" s="2">
+        <v>0.10002</v>
+      </c>
+      <c r="NV28" s="2">
+        <f t="shared" si="104"/>
+        <v>0.67862944904660294</v>
+      </c>
+      <c r="NW28" s="2">
+        <v>0.83550000000000002</v>
+      </c>
+      <c r="NY28" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="NZ28" s="2">
+        <f t="shared" si="105"/>
+        <v>0.27030311213123615</v>
+      </c>
+      <c r="OA28" s="2">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="OG28" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="OH28" s="2">
+        <f t="shared" si="107"/>
+        <v>0.91094688450035832</v>
+      </c>
+      <c r="OI28" s="2">
+        <v>0.432</v>
+      </c>
+      <c r="OK28" s="2">
+        <v>0.87</v>
+      </c>
+      <c r="OL28" s="2">
+        <f t="shared" si="108"/>
+        <v>0.94479508095283549</v>
+      </c>
+      <c r="OM28" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="PA28" s="2">
+        <v>1.8406</v>
+      </c>
+      <c r="PB28" s="2">
+        <f t="shared" si="112"/>
+        <v>0.24902513850499722</v>
+      </c>
+      <c r="PC28" s="2">
+        <v>0.96640000000000004</v>
+      </c>
     </row>
-    <row r="29" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:419" ht="49" customHeight="1">
       <c r="A29" s="2">
         <v>23</v>
       </c>
@@ -19659,7 +21801,7 @@
         <v>4.5</v>
       </c>
       <c r="DQ29" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.32375545644816078</v>
       </c>
       <c r="DR29" s="2">
@@ -20006,8 +22148,38 @@
         <f t="shared" si="94"/>
         <v>0.6753258937161507</v>
       </c>
+      <c r="OG29" s="2">
+        <v>0.83</v>
+      </c>
+      <c r="OH29" s="2">
+        <f t="shared" si="107"/>
+        <v>0.92584741402375026</v>
+      </c>
+      <c r="OI29" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="OK29" s="2">
+        <v>0.89</v>
+      </c>
+      <c r="OL29" s="2">
+        <f t="shared" si="108"/>
+        <v>0.95389790840534661</v>
+      </c>
+      <c r="OM29" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="PA29" s="2">
+        <v>2.3864000000000001</v>
+      </c>
+      <c r="PB29" s="2">
+        <f t="shared" si="112"/>
+        <v>0.30066693771697228</v>
+      </c>
+      <c r="PC29" s="2">
+        <v>0.95609999999999995</v>
+      </c>
     </row>
-    <row r="30" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:419" ht="49" customHeight="1">
       <c r="A30" s="2">
         <v>24</v>
       </c>
@@ -20049,7 +22221,7 @@
         <v>5</v>
       </c>
       <c r="DQ30" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.34723718137014914</v>
       </c>
       <c r="DR30" s="2">
@@ -20382,8 +22554,38 @@
         <f t="shared" si="94"/>
         <v>0.63427712089397181</v>
       </c>
+      <c r="OG30" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="OH30" s="2">
+        <f t="shared" si="107"/>
+        <v>0.93544823138067557</v>
+      </c>
+      <c r="OI30" s="2">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="OK30" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="OL30" s="2">
+        <f t="shared" si="108"/>
+        <v>0.96276614678361838</v>
+      </c>
+      <c r="OM30" s="2">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="PA30" s="2">
+        <v>2.9451999999999998</v>
+      </c>
+      <c r="PB30" s="2">
+        <f t="shared" si="112"/>
+        <v>0.34666452693201438</v>
+      </c>
+      <c r="PC30" s="2">
+        <v>0.94530000000000003</v>
+      </c>
     </row>
-    <row r="31" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:419" ht="49" customHeight="1">
       <c r="A31" s="2">
         <v>25</v>
       </c>
@@ -20422,7 +22624,7 @@
         <v>5.5</v>
       </c>
       <c r="DQ31" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.36914288598203948</v>
       </c>
       <c r="DR31" s="2">
@@ -20719,8 +22921,50 @@
         <f t="shared" si="76"/>
         <v>0.33964324733851287</v>
       </c>
+      <c r="OG31" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="OH31" s="2">
+        <f t="shared" si="107"/>
+        <v>0.94937639625884596</v>
+      </c>
+      <c r="OI31" s="2">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="OK31" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="OL31" s="2">
+        <f t="shared" si="108"/>
+        <v>0.97564811080796721</v>
+      </c>
+      <c r="OM31" s="2">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="PA31" s="2">
+        <v>3.6261999999999999</v>
+      </c>
+      <c r="PB31" s="2">
+        <f t="shared" si="112"/>
+        <v>0.39514770260839016</v>
+      </c>
+      <c r="PC31" s="2">
+        <v>0.93200000000000005</v>
+      </c>
     </row>
-    <row r="32" spans="1:379" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:419" ht="49" customHeight="1">
+      <c r="A32" s="2">
+        <v>26</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D32" s="2">
+        <v>2004</v>
+      </c>
       <c r="AY32" s="2">
         <v>11.013</v>
       </c>
@@ -20747,7 +22991,7 @@
         <v>6</v>
       </c>
       <c r="DQ32" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.38962608493963408</v>
       </c>
       <c r="DR32" s="2">
@@ -21027,8 +23271,53 @@
         <f t="shared" si="76"/>
         <v>0.30187865749786363</v>
       </c>
+      <c r="OG32" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="OH32" s="2">
+        <f t="shared" si="107"/>
+        <v>0.96276614678361838</v>
+      </c>
+      <c r="OI32" s="2">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="OK32" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="OL32" s="2">
+        <f t="shared" si="108"/>
+        <v>0.99208286730727391</v>
+      </c>
+      <c r="OM32" s="2">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="PA32" s="2">
+        <v>4.8470000000000004</v>
+      </c>
+      <c r="PB32" s="2">
+        <f t="shared" si="112"/>
+        <v>0.46616429737569781</v>
+      </c>
+      <c r="PC32" s="2">
+        <v>0.90759999999999996</v>
+      </c>
     </row>
-    <row r="33" spans="51:314" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:403" ht="49" customHeight="1">
+      <c r="A33" s="2">
+        <v>27</v>
+      </c>
+      <c r="B33" t="s">
+        <v>480</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D33" s="2">
+        <v>1996</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>482</v>
+      </c>
       <c r="AY33" s="2">
         <v>11.999000000000001</v>
       </c>
@@ -21055,7 +23344,7 @@
         <v>6.5</v>
       </c>
       <c r="DQ33" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.40882098212570239</v>
       </c>
       <c r="DR33" s="2">
@@ -21321,8 +23610,40 @@
         <f t="shared" si="76"/>
         <v>0.26882834670003947</v>
       </c>
+      <c r="OG33" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="OH33" s="2">
+        <f t="shared" si="107"/>
+        <v>0.97564811080796721</v>
+      </c>
+      <c r="OI33" s="2">
+        <v>0.156</v>
+      </c>
+      <c r="OK33" s="2">
+        <v>1</v>
+      </c>
+      <c r="OL33" s="2">
+        <f t="shared" si="108"/>
+        <v>1</v>
+      </c>
+      <c r="OM33" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="51:314" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:403" ht="49" customHeight="1">
+      <c r="A34" s="2">
+        <v>28</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D34" s="2">
+        <v>2006</v>
+      </c>
       <c r="HD34" s="2">
         <v>0.8</v>
       </c>
@@ -21565,8 +23886,33 @@
         <f t="shared" si="76"/>
         <v>0.23925417759106679</v>
       </c>
+      <c r="OG34" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="OH34" s="2">
+        <f t="shared" si="107"/>
+        <v>0.98805063638182689</v>
+      </c>
+      <c r="OI34" s="2">
+        <v>6.3E-2</v>
+      </c>
     </row>
-    <row r="35" spans="51:314" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:403" ht="49" customHeight="1">
+      <c r="A35" s="2">
+        <v>29</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D35" s="2">
+        <v>2017</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>492</v>
+      </c>
       <c r="HD35" s="2">
         <v>0.9</v>
       </c>
@@ -21795,8 +24141,30 @@
       <c r="KH35" s="2">
         <v>-7462</v>
       </c>
+      <c r="OG35" s="2">
+        <v>1</v>
+      </c>
+      <c r="OH35" s="2">
+        <f t="shared" si="107"/>
+        <v>1</v>
+      </c>
+      <c r="OI35" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="51:314" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:403" ht="49" customHeight="1">
+      <c r="A36" s="2">
+        <v>30</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D36" s="2">
+        <v>2016</v>
+      </c>
       <c r="HD36" s="2">
         <v>1</v>
       </c>
@@ -22026,7 +24394,7 @@
         <v>-8515</v>
       </c>
     </row>
-    <row r="37" spans="51:314" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:403" ht="49" customHeight="1">
       <c r="HD37" s="2">
         <v>1.25</v>
       </c>
@@ -22256,7 +24624,7 @@
         <v>-11243</v>
       </c>
     </row>
-    <row r="38" spans="51:314" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:403" ht="49" customHeight="1">
       <c r="HD38" s="2">
         <v>1.5</v>
       </c>
@@ -22486,7 +24854,7 @@
         <v>-14079</v>
       </c>
     </row>
-    <row r="39" spans="51:314" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:403" ht="49" customHeight="1">
       <c r="HD39" s="2">
         <v>1.75</v>
       </c>
@@ -22716,7 +25084,7 @@
         <v>-16996</v>
       </c>
     </row>
-    <row r="40" spans="51:314" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:403" ht="49" customHeight="1">
       <c r="HD40" s="2">
         <v>2</v>
       </c>
@@ -22927,7 +25295,7 @@
         <v>-19972</v>
       </c>
     </row>
-    <row r="41" spans="51:314" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:403" ht="49" customHeight="1">
       <c r="HD41" s="2">
         <v>2.25</v>
       </c>
@@ -23119,7 +25487,7 @@
         <v>-22991</v>
       </c>
     </row>
-    <row r="42" spans="51:314" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:403" ht="49" customHeight="1">
       <c r="HD42" s="2">
         <v>2.5</v>
       </c>
@@ -23311,7 +25679,7 @@
         <v>-26037</v>
       </c>
     </row>
-    <row r="43" spans="51:314" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:403" ht="49" customHeight="1">
       <c r="HD43" s="2">
         <v>2.75</v>
       </c>
@@ -23322,7 +25690,7 @@
         <v>0.40479999999999999</v>
       </c>
       <c r="HG43" s="2">
-        <f t="shared" ref="HG43:HG45" si="105">$HD$2*HD43/(1+$HD$2*HD43)</f>
+        <f t="shared" ref="HG43:HG45" si="115">$HD$2*HD43/(1+$HD$2*HD43)</f>
         <v>0.26640754041349396</v>
       </c>
       <c r="HH43" s="2">
@@ -23465,7 +25833,7 @@
         <v>-29098</v>
       </c>
     </row>
-    <row r="44" spans="51:314" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:403" ht="49" customHeight="1">
       <c r="HD44" s="2">
         <v>3</v>
       </c>
@@ -23476,7 +25844,7 @@
         <v>0.3982</v>
       </c>
       <c r="HG44" s="2">
-        <f t="shared" si="105"/>
+        <f t="shared" si="115"/>
         <v>0.28375420234839094</v>
       </c>
       <c r="HH44" s="2">
@@ -23600,7 +25968,7 @@
         <v>-32165</v>
       </c>
     </row>
-    <row r="45" spans="51:314" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:403" ht="49" customHeight="1">
       <c r="HD45" s="2">
         <v>3.1070000000000002</v>
       </c>
@@ -23611,7 +25979,7 @@
         <v>0.39550000000000002</v>
       </c>
       <c r="HG45" s="2">
-        <f t="shared" si="105"/>
+        <f t="shared" si="115"/>
         <v>0.29093038854005598</v>
       </c>
       <c r="HH45" s="2">
@@ -23697,7 +26065,7 @@
         <v>-35228</v>
       </c>
     </row>
-    <row r="46" spans="51:314" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:403" ht="49" customHeight="1">
       <c r="HR46" s="2">
         <v>3.5</v>
       </c>
@@ -23775,7 +26143,7 @@
         <v>-36720</v>
       </c>
     </row>
-    <row r="47" spans="51:314" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:403" ht="49" customHeight="1">
       <c r="HR47" s="2">
         <v>3.75</v>
       </c>
@@ -23834,7 +26202,7 @@
         <v>-40566</v>
       </c>
     </row>
-    <row r="48" spans="51:314" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:403" ht="49" customHeight="1">
       <c r="HR48" s="2">
         <v>3.806</v>
       </c>
@@ -23893,7 +26261,7 @@
         <v>-43370</v>
       </c>
     </row>
-    <row r="49" spans="240:259" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="240:259" ht="49" customHeight="1">
       <c r="IF49" s="2">
         <v>4.25</v>
       </c>
@@ -23933,7 +26301,7 @@
         <v>-43946</v>
       </c>
     </row>
-    <row r="50" spans="240:259" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="240:259" ht="49" customHeight="1">
       <c r="IF50" s="2">
         <v>4.5</v>
       </c>
@@ -23954,7 +26322,7 @@
         <v>14038</v>
       </c>
     </row>
-    <row r="51" spans="240:259" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="240:259" ht="49" customHeight="1">
       <c r="IF51" s="2">
         <v>4.75</v>
       </c>
@@ -23975,7 +26343,7 @@
         <v>17314</v>
       </c>
     </row>
-    <row r="52" spans="240:259" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="240:259" ht="49" customHeight="1">
       <c r="IF52" s="2">
         <v>5</v>
       </c>
@@ -23996,7 +26364,7 @@
         <v>20824</v>
       </c>
     </row>
-    <row r="53" spans="240:259" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="240:259" ht="49" customHeight="1">
       <c r="IF53" s="2">
         <v>5.25</v>
       </c>
@@ -24017,7 +26385,7 @@
         <v>24566</v>
       </c>
     </row>
-    <row r="54" spans="240:259" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="240:259" ht="49" customHeight="1">
       <c r="IF54" s="2">
         <v>5.5</v>
       </c>
@@ -24058,9 +26426,10 @@
     <hyperlink ref="B21" r:id="rId16" xr:uid="{00000000-0004-0000-0300-00000F000000}"/>
     <hyperlink ref="B22" r:id="rId17" xr:uid="{00000000-0004-0000-0300-000010000000}"/>
     <hyperlink ref="B24" r:id="rId18" xr:uid="{94628BD9-B85F-5E41-9236-27B0F364856F}"/>
+    <hyperlink ref="B32" r:id="rId19" display="https://link.springer.com/article/10.1007/s00217-004-0974-6" xr:uid="{9D156998-8D24-E84E-BA69-9B088F7499DF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId19"/>
-  <drawing r:id="rId20"/>
+  <pageSetup orientation="portrait" r:id="rId20"/>
+  <drawing r:id="rId21"/>
 </worksheet>
 </file>